--- a/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_reumatologica.xlsx
+++ b/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_reumatologica.xlsx
@@ -416,22 +416,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>903</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>297</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -443,22 +443,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>218 (47,6%)</t>
+          <t>425 (47,1%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>76 (53,1%)</t>
+          <t>137 (46,1%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60 (39,0%)</t>
+          <t>130 (46,4%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>82 (50,9%)</t>
+          <t>158 (48,5%)</t>
         </is>
       </c>
     </row>
@@ -470,22 +470,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>169 (36,9%)</t>
+          <t>297 (32,9%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>61 (42,7%)</t>
+          <t>106 (35,7%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45 (29,2%)</t>
+          <t>89 (31,8%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>63 (39,1%)</t>
+          <t>102 (31,3%)</t>
         </is>
       </c>
     </row>
@@ -497,22 +497,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>138 (30,1%)</t>
+          <t>291 (32,2%)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>34 (23,8%)</t>
+          <t>83 (27,9%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48 (31,2%)</t>
+          <t>103 (36,8%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>56 (34,8%)</t>
+          <t>105 (32,2%)</t>
         </is>
       </c>
     </row>
@@ -524,22 +524,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>151 (33,0%)</t>
+          <t>315 (34,9%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48 (33,6%)</t>
+          <t>108 (36,4%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>61 (39,6%)</t>
+          <t>88 (31,4%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42 (26,1%)</t>
+          <t>119 (36,5%)</t>
         </is>
       </c>
     </row>
@@ -551,22 +551,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>32 (7,0%)</t>
+          <t>607 (67,2%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7 (4,9%)</t>
+          <t>202 (68,0%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12 (7,8%)</t>
+          <t>197 (70,4%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13 (8,1%)</t>
+          <t>208 (63,8%)</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A10BH 175 (38,2%)</t>
+          <t>J10JE54 75 (8,3%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A10BJ 57 (39,9%)</t>
+          <t>M10ME56 26 (8,8%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A10BD07 66 (42,9%)</t>
+          <t>J10JE56 25 (8,9%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A10BH 64 (39,8%)</t>
+          <t>B10BD21 30 (9,2%)</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A10BJ 175 (38,2%)</t>
+          <t>M10ME56 69 (7,6%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A10BD24 57 (39,9%)</t>
+          <t>B10BH02 26 (8,8%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A10AE56 66 (42,9%)</t>
+          <t>J10JE54 25 (8,9%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A10AE54 63 (39,1%)</t>
+          <t>B10BD07 28 (8,6%)</t>
         </is>
       </c>
     </row>
@@ -639,22 +639,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A10AE56 174 (38,0%)</t>
+          <t>M10BD24 66 (7,3%)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A10AE56 57 (39,9%)</t>
+          <t>C10BK02 26 (8,8%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A10BD15 65 (42,2%)</t>
+          <t>M10ME56 25 (8,9%)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A10BD16 63 (39,1%)</t>
+          <t>C10BD10 28 (8,6%)</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A10BD16 174 (38,0%)</t>
+          <t>C10BD24 64 (7,1%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A10BD16 55 (38,5%)</t>
+          <t>A10BD10 24 (8,1%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A10BK 65 (42,2%)</t>
+          <t>D10BD19 24 (8,6%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A10BD20 62 (38,5%)</t>
+          <t>J10JE54 28 (8,6%)</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A10BD15 173 (37,8%)</t>
+          <t>B10BD07 63 (7,0%)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A10BD07 55 (38,5%)</t>
+          <t>A10BD20 24 (8,1%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A10BH 60 (39,0%)</t>
+          <t>M10BD24 24 (8,6%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A10BJ 61 (37,9%)</t>
+          <t>C10BD24 28 (8,6%)</t>
         </is>
       </c>
     </row>
@@ -727,22 +727,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A10BD 456 (99,6%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD M10BD 5 (0,6%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A10BD 143 (100,0%)</t>
+          <t>A10BD B10BD C10BD J10BD M10BD 2 (0,7%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A10BD 153 (99,4%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD 3 (1,1%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A10BD 160 (99,4%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD M10BD 3 (0,9%)</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A10AE 240 (52,4%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD 4 (0,4%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A10AE 69 (48,3%)</t>
+          <t>A10BD B10BD B10BX C10BD C10BJ D10BD J10BJ M10BD 1 (0,3%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A10AE 84 (54,5%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 2 (0,7%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A10AE 87 (54,0%)</t>
+          <t>A10BD C10BD D10BX J10BD M10BD 2 (0,6%)</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A10BJ 152 (33,2%)</t>
+          <t>A10BD B10BD C10BD J10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A10BJ 50 (35,0%)</t>
+          <t>A10BD A10BJ B10BE M10BX M10ME 1 (0,3%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A10BK 54 (35,1%)</t>
+          <t>A10BD B10BD D10BD J10BD M10BD 2 (0,7%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A10BH 54 (33,5%)</t>
+          <t>A10BD B10BD B10BH C10BD D10BK M10BK M10BX 1 (0,3%)</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A10BH 141 (30,8%)</t>
+          <t>A10BD B10BD C10BD J10JE M10BD 2 (0,2%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A10BX 49 (34,3%)</t>
+          <t>A10BD A10BH A10BX B10BD B10BK C10BD D10BD J10BD J10JE 1 (0,3%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A10BJ 49 (31,8%)</t>
+          <t>A10BD B10BD B10BE B10BJ C10BD D10BD D10DE 1 (0,4%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A10BJ 53 (32,9%)</t>
+          <t>A10BD B10BJ D10BD D10BK M10ME 1 (0,3%)</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A10BK 137 (29,9%)</t>
+          <t>A10BD A10BH B10BD C10BD D10BD 2 (0,2%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A10BH 44 (30,8%)</t>
+          <t>A10BD C10BD J10BD M10BD M10ME 1 (0,3%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A10BH 43 (27,9%)</t>
+          <t>A10BH B10BD C10CE D10BD J10BD 1 (0,4%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A10BX 42 (26,1%)</t>
+          <t>A10BD C10BD J10BJ M10BD M10ME 1 (0,3%)</t>
         </is>
       </c>
     </row>

--- a/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_reumatologica.xlsx
+++ b/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_reumatologica.xlsx
@@ -585,22 +585,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J10JE54 75 (8,3%)</t>
+          <t>NA 75 (8,3%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M10ME56 26 (8,8%)</t>
+          <t>NA 26 (8,8%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>J10JE56 25 (8,9%)</t>
+          <t>NA 25 (8,9%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>B10BD21 30 (9,2%)</t>
+          <t>NA 30 (9,2%)</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M10ME56 69 (7,6%)</t>
+          <t>NA 69 (7,6%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B10BH02 26 (8,8%)</t>
+          <t>NA 26 (8,8%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>J10JE54 25 (8,9%)</t>
+          <t>NA 25 (8,9%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B10BD07 28 (8,6%)</t>
+          <t>NA 28 (8,6%)</t>
         </is>
       </c>
     </row>
@@ -639,22 +639,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M10BD24 66 (7,3%)</t>
+          <t>NA 66 (7,3%)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C10BK02 26 (8,8%)</t>
+          <t>NA 26 (8,8%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M10ME56 25 (8,9%)</t>
+          <t>NA 25 (8,9%)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C10BD10 28 (8,6%)</t>
+          <t>NA 28 (8,6%)</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C10BD24 64 (7,1%)</t>
+          <t>NA 64 (7,1%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A10BD10 24 (8,1%)</t>
+          <t>jj 24 (8,1%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>D10BD19 24 (8,6%)</t>
+          <t>NA 24 (8,6%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>J10JE54 28 (8,6%)</t>
+          <t>NA 28 (8,6%)</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B10BD07 63 (7,0%)</t>
+          <t>NA 63 (7,0%)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A10BD20 24 (8,1%)</t>
+          <t>rr 24 (8,1%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M10BD24 24 (8,6%)</t>
+          <t>NA 24 (8,6%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C10BD24 28 (8,6%)</t>
+          <t>NA 28 (8,6%)</t>
         </is>
       </c>
     </row>
@@ -727,22 +727,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD M10BD 5 (0,6%)</t>
+          <t>e B10BD C10BD D10BD M10BD 186 (3,7%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD M10BD 2 (0,7%)</t>
+          <t>e B10BD C10BD D10BD M10BD 62 (3,7%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD 3 (1,1%)</t>
+          <t>e B10BD C10BD D10BD M10BD 66 (4,1%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD M10BD 3 (0,9%)</t>
+          <t>e B10BD C10BD J10BD M10BD 71 (4,2%)</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD 4 (0,4%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 178 (3,6%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A10BD B10BD B10BX C10BD C10BJ D10BD J10BJ M10BD 1 (0,3%)</t>
+          <t>e B10BD C10BD D10BD J10BD 54 (3,2%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 2 (0,7%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 62 (3,8%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A10BD C10BD D10BX J10BD M10BD 2 (0,6%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 65 (3,8%)</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD M10BD 3 (0,3%)</t>
+          <t>e B10BD C10BD J10BD M10BD 175 (3,5%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A10BD A10BJ B10BE M10BX M10ME 1 (0,3%)</t>
+          <t>e B10BD C10BD J10BD M10BD 52 (3,1%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A10BD B10BD D10BD J10BD M10BD 2 (0,7%)</t>
+          <t>e B10BD C10BD D10BD J10BD 57 (3,5%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A10BD B10BD B10BH C10BD D10BK M10BK M10BX 1 (0,3%)</t>
+          <t>e B10BD C10BD D10BD J10BD 62 (3,7%)</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10JE M10BD 2 (0,2%)</t>
+          <t>e B10BD C10BD D10BD J10BD 173 (3,5%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A10BD A10BH A10BX B10BD B10BK C10BD D10BD J10BD J10JE 1 (0,3%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 51 (3,0%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A10BD B10BD B10BE B10BJ C10BD D10BD D10DE 1 (0,4%)</t>
+          <t>e C10BD D10BD J10BD M10BD 55 (3,4%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A10BD B10BJ D10BD D10BK M10ME 1 (0,3%)</t>
+          <t>e B10BD D10BD J10BD M10BD 59 (3,5%)</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A10BD A10BH B10BD C10BD D10BD 2 (0,2%)</t>
+          <t>e B10BD D10BD J10BD M10BD 162 (3,2%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A10BD C10BD J10BD M10BD M10ME 1 (0,3%)</t>
+          <t>e B10BD D10BD J10BD M10BD 50 (3,0%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A10BH B10BD C10CE D10BD J10BD 1 (0,4%)</t>
+          <t>e B10BD D10BD J10BD M10BD 53 (3,3%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A10BD C10BD J10BJ M10BD M10ME 1 (0,3%)</t>
+          <t>e B10BD C10BD D10BD M10BD 58 (3,4%)</t>
         </is>
       </c>
     </row>

--- a/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_reumatologica.xlsx
+++ b/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_reumatologica.xlsx
@@ -727,22 +727,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 186 (3,7%)</t>
+          <t>e B10BD C10BD D10BD J10BD 37 (4,1%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 62 (3,7%)</t>
+          <t>e B10BD C10BD D10BD J10BD 10 (3,4%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 66 (4,1%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 10 (3,6%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD J10BD M10BD 71 (4,2%)</t>
+          <t>e B10BD C10BD D10BD J10BD 18 (5,5%)</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 178 (3,6%)</t>
+          <t>e B10BD C10BD D10BD M10BD 34 (3,8%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 54 (3,2%)</t>
+          <t>e B10BD C10BD D10BD M10BD 10 (3,4%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 62 (3,8%)</t>
+          <t>e B10BD C10BD D10BD J10BD 9 (3,2%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 65 (3,8%)</t>
+          <t>e B10BD C10BD D10BD M10BD 16 (4,9%)</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD J10BD M10BD 175 (3,5%)</t>
+          <t>e B10BD C10BD J10BD M10BD 34 (3,8%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD J10BD M10BD 52 (3,1%)</t>
+          <t>e B10BD C10BD J10BD M10BD 10 (3,4%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 57 (3,5%)</t>
+          <t>e B10BD C10BD D10BD M10BD 8 (2,9%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 62 (3,7%)</t>
+          <t>e B10BD C10BD J10BD M10BD 16 (4,9%)</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 173 (3,5%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 34 (3,8%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 51 (3,0%)</t>
+          <t>e C10BD D10BD J10BD M10BD 8 (2,7%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>e C10BD D10BD J10BD M10BD 55 (3,4%)</t>
+          <t>e B10BD C10BD J10BD M10BD 8 (2,9%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 59 (3,5%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 16 (4,9%)</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 162 (3,2%)</t>
+          <t>e C10BD D10BD J10BD M10BD 30 (3,3%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 50 (3,0%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 8 (2,7%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 53 (3,3%)</t>
+          <t>e B10BD C10BD D10BD D10DE 7 (2,5%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 58 (3,4%)</t>
+          <t>e C10BD D10BD J10BD M10BD 15 (4,6%)</t>
         </is>
       </c>
     </row>
